--- a/android/app/src/main/assets/public/files/event/event.xlsx
+++ b/android/app/src/main/assets/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1234DE9A-39E1-4665-B9B1-DE31190785CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F14163-1E5F-4E01-BB6E-5DEDBFC26972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="525" windowWidth="26205" windowHeight="14850" firstSheet="4" activeTab="12" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26205" windowHeight="14850" firstSheet="5" activeTab="13" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="2R1201ev" sheetId="13" r:id="rId11"/>
     <sheet name="Sheet3" sheetId="9" r:id="rId12"/>
     <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
+    <sheet name="DOJO" sheetId="16" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="344">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1437,10 +1438,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>（プロセルが不透明度50%で左から出てくる。）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>うなだれていた首をもたげると、視界の中央に、それはいた。白い長髪、黒い角、背の翼。明らかに人ではない姿。</t>
     <rPh sb="7" eb="8">
       <t>クビ</t>
@@ -1660,6 +1657,242 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（プロセル"C:\Users\user\.antigravity\game\files\CHR\010001b.png"が不透明度50%で左から出てくる。）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM:"C:\Users\user\.antigravity\game\files\BGM\002_menu.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像：C:\Users\user\.antigravity\game\files\MAP\dojo.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>眼を開けるとそこは何かの道場のようで、中央に道着を着たプロセルが立っていた</t>
+    <rPh sb="0" eb="1">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ドウギ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よく来たな、ここは貴様らを鍛え直すDOJOだ</t>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ど、道場…？</t>
+    <rPh sb="2" eb="4">
+      <t>ドウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NO！　DOJO！　貴様らはここで心・技・体を鍛え上げ最強の魔法少女となるのだ</t>
+    <rPh sb="10" eb="12">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カラダ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>キタ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サイキョウ</t>
+    </rPh>
+    <rPh sb="30" eb="34">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ド、DOJO…？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>All Right！ DOJO！　貴様らが溜め込んだSPをより効率よく使用し、貴様らを作り変え…鍛え上げるのだ</t>
+    <rPh sb="17" eb="19">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キタ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちょっと待て作り変えって何だ</t>
+    <rPh sb="4" eb="5">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセルの残した、道場と書いた札を見つめていると紫苑は突如めまいに襲われ、視界は暗闇に包まれた。</t>
+    <rPh sb="5" eb="6">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トツジョ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シカイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>クラヤミ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ツツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分け身の分け身である余にはそれを説明する分の知識を与えられていない、早く強くなって余の本体を解放してくれ。</t>
+    <rPh sb="0" eb="1">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カイホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2448,7 +2681,7 @@
         <v>257</v>
       </c>
       <c r="C1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G1" t="s">
         <v>274</v>
@@ -2466,17 +2699,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2486,7 +2719,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2511,12 +2744,12 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -2536,12 +2769,12 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -2566,17 +2799,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -2586,17 +2819,17 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -2611,7 +2844,7 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -2621,12 +2854,12 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -2656,7 +2889,7 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -2671,7 +2904,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -2732,6 +2965,107 @@
     <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>310</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894D19D9-00DC-4DED-8255-C52D5A226D4C}">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/android/app/src/main/assets/public/files/event/event.xlsx
+++ b/android/app/src/main/assets/public/files/event/event.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F14163-1E5F-4E01-BB6E-5DEDBFC26972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8651142-82C7-4F56-B4A7-2BB636C18AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="26205" windowHeight="14850" firstSheet="5" activeTab="13" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>

--- a/android/app/src/main/assets/public/files/event/event.xlsx
+++ b/android/app/src/main/assets/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8651142-82C7-4F56-B4A7-2BB636C18AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9D892-94F6-4946-9C78-3459259E8181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="26205" windowHeight="14850" firstSheet="5" activeTab="13" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="3075" yWindow="360" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="Sheet3" sheetId="9" r:id="rId12"/>
     <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
     <sheet name="DOJO" sheetId="16" r:id="rId14"/>
+    <sheet name="JIKU" sheetId="17" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="363">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -1893,6 +1894,295 @@
     </rPh>
     <rPh sb="46" eb="48">
       <t>カイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景：C:\Users\user\.antigravity\game\files\MAP\m(k,11)r.jpg</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑が右に出てくる</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「……」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左側から不透明度50%のプロセル"C:\Users\user\.antigravity\game\files\CHR\010001b.png"が出てくる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダリガワ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>フトウメイド</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「これはヒトが造った時空を超える装置だ」</t>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ソウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「うわっ！……はあ…はあ…」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「貴様がここを訪れたことで余が造っていた平行時空との接続が完了した。」</t>
+    <rPh sb="5" eb="7">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オトズ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヘイコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「……？」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「招待しよう、何はともあれ時空の館へ」</t>
+    <rPh sb="5" eb="7">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヤカタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗転</t>
+    <rPh sb="0" eb="2">
+      <t>アンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一枚絵(背景ではなくイベントグラフィック)　C:\Users\user\.antigravity\game\files\MAP\jiku-.jpg</t>
+    <rPh sb="0" eb="3">
+      <t>イチマイエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「ここは現在世界の時空をゆがめている輩のスキをついて余が造った避難所、訓練施設」</t>
+    <rPh sb="8" eb="10">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヤカラ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ヒナンジョ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラの立ち絵は表示しない。</t>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「地上とここでは貴様らの成長度合いは共有されない。レリクスと宝石が頼りだ。」</t>
+    <rPh sb="5" eb="7">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キサマ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドア</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ホウセキ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「用意された幻影を倒すことで道場で訓練に使うSPといくらかのレリクスが見つけられるはずだ」</t>
+    <rPh sb="5" eb="7">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンエイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「……」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル「例によって話せる時間は少ない…あとは使って覚えろ。」</t>
+    <rPh sb="5" eb="6">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「…地上来て楽しんでんなコイツ…」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>道場解放後に地上、シルバードームに到達するとイベントが始まる。</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウタツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ハジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3074,6 +3364,122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF88277-A34F-4C4C-8EFC-0E2C09FF6627}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>

--- a/android/app/src/main/assets/public/files/event/event.xlsx
+++ b/android/app/src/main/assets/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9D892-94F6-4946-9C78-3459259E8181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9AD9A1-4F95-4685-82F2-B08F41F209FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="360" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="675" yWindow="315" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="2RDEVIL" sheetId="14" r:id="rId13"/>
     <sheet name="DOJO" sheetId="16" r:id="rId14"/>
     <sheet name="JIKU" sheetId="17" r:id="rId15"/>
+    <sheet name="Sheet2" sheetId="18" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="377">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -2183,6 +2184,209 @@
     </rPh>
     <rPh sb="27" eb="28">
       <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天隕晶</t>
+    <rPh sb="0" eb="1">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アキラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>七星宝剣</t>
+    <rPh sb="0" eb="1">
+      <t>ナナ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱点属性の敵への攻撃のダメージを2倍にする。</t>
+    <rPh sb="0" eb="2">
+      <t>ジャクテン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+5 CH率+5 CH倍率+5</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在精神力の1/10を攻撃力に加算する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理攻撃には適用されない。</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理攻撃にのみ適用される。</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精神力+5 リロード+5 CH率+5</t>
+    <rPh sb="0" eb="3">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在生命力の1/10を攻撃力に加算する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生命力+5 回避+5 CH倍率+5</t>
+    <rPh sb="0" eb="3">
+      <t>セイメイリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バイリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妙見鑑</t>
+    <rPh sb="0" eb="2">
+      <t>ミョウケン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェイスエリアの奥深くにあるスターストーンを見てからスカイツリーに行くと手に入る。</t>
+    <rPh sb="8" eb="10">
+      <t>オクフカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スケルトンエリアを下った先にあるキャリバーンを見てから上野にいくと手に入る。</t>
+    <rPh sb="9" eb="10">
+      <t>クダ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ウエノ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地下21階にある。</t>
+    <rPh sb="0" eb="2">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3480,6 +3684,87 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27536E43-80CF-4D3F-9264-77E06E30D30F}">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>372</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>

--- a/android/app/src/main/assets/public/files/event/event.xlsx
+++ b/android/app/src/main/assets/public/files/event/event.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9AD9A1-4F95-4685-82F2-B08F41F209FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A4CCDE-42AC-4980-96CB-C01EE53B91B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="315" windowWidth="26205" windowHeight="14850" firstSheet="6" activeTab="14" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
+    <workbookView xWindow="1320" yWindow="420" windowWidth="26205" windowHeight="14850" firstSheet="8" activeTab="16" xr2:uid="{77204450-B393-4813-8750-11762B8571B3}"/>
   </bookViews>
   <sheets>
     <sheet name="1207event" sheetId="3" r:id="rId1"/>
@@ -29,6 +29,8 @@
     <sheet name="DOJO" sheetId="16" r:id="rId14"/>
     <sheet name="JIKU" sheetId="17" r:id="rId15"/>
     <sheet name="Sheet2" sheetId="18" r:id="rId16"/>
+    <sheet name="塔21F" sheetId="19" r:id="rId17"/>
+    <sheet name="塔21Fb" sheetId="20" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="408">
   <si>
     <t>今日は12月14日。</t>
     <rPh sb="0" eb="2">
@@ -2388,6 +2390,166 @@
     <rPh sb="4" eb="5">
       <t>カイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ曲が演奏中でなければ　bgm："C:\Users\user\.antigravity\game\files\BGM\tow_Frozen Silence.mp3"</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キョク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>エンソウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント一枚絵："C:\Users\user\.antigravity\game\files\event\tow_21.jpg"</t>
+    <rPh sb="4" eb="7">
+      <t>イチマイエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凍てつくような冷気が肺を刺す。巨大な神殿のような広間へ足を踏み入れた紫苑は、その異様な光景に思わず足を止めた。</t>
+  </si>
+  <si>
+    <t>その時、鼓膜ではなく紫苑の脳内に直接、あの傲慢で冷ややかな声が響き渡った。</t>
+  </si>
+  <si>
+    <t>『――よくたどり着いた、人の子よ』</t>
+  </si>
+  <si>
+    <t>紫苑が手にした武器を強く握り直し、腰を落として身構えたその瞬間――氷像の周囲の大気が急激に圧縮され、けたたましい音鳴りと共に防衛機構が作動した。</t>
+  </si>
+  <si>
+    <t>視界を白く染め上げるほどの猛吹雪と、不可視の氷の刃が、侵入者をミンチにせんと全方位から殺意を持って吹き荒れる。</t>
+  </si>
+  <si>
+    <t>殺戮の嵐が吹き荒れる中、プロセルの声だけは他人事のようにひどく呑気だった。</t>
+  </si>
+  <si>
+    <t>紫苑は口元を歪めて悪態をつくと、凍てつく床を強く蹴り飛ばした。吹き荒れる死の吹雪を掻き分け、その中心にある巨大な氷の塊を粉砕するための死闘が幕を開ける。</t>
+  </si>
+  <si>
+    <t>紫苑「うおっ……でっか……」</t>
+    <rPh sb="0" eb="2">
+      <t>シオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広間の中央には、荘厳で巨大な悪魔の氷像が鎮座していた。分厚い氷に閉ざされたその姿は、透き通るような神々しさと、背筋が凍るほどの魔性を同時に放ち、絶対的な静寂の中で眠りについている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「……本当に、いいんだな？」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑「言ってくれる……ッ！」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル『それが余の力を封じている原因だ。さあ、その忌まわしい氷像を砕け！』</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル『反撃をかわして、うまく壊せ』</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>声の主は日ごろ世話になっている道場主、いや時空館のメイド…もとい悪魔プロセルだった。</t>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セワ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ドウジョウヌシ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジクウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヤカタ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>アクマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm："C:\Users\user\.antigravity\game\files\BGM\005_JOIN_US.mp3"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一枚絵："C:\Users\user\.antigravity\game\files\event\tow_21b.jpg"</t>
+    <rPh sb="0" eb="3">
+      <t>イチマイエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の瞬間、巨大な氷像は無数の破片となって吹き飛び、ダイヤモンドダストのようにきらきらと宙を舞う。</t>
+  </si>
+  <si>
+    <t>その眩い光の粉の只中から、プロセルが優雅に舞い降りた。</t>
+  </si>
+  <si>
+    <t>「素晴らしい。よくぞ砕いてみせたな、我が麗しの主よ」</t>
+  </si>
+  <si>
+    <t>疲労で重くなった顔を上げ、紫苑が短く告げると、プロセルは不満げに目を細めた。</t>
+  </si>
+  <si>
+    <t>ふわりと冷たい香りを漂わせて紫苑の耳元へと近づき、甘く囁く。</t>
+  </si>
+  <si>
+    <t>「早まるな。この不可解な塔の正体も、余が封じられていた理由も、まだ何一つ判明してはおらぬ。当然、契約は継続だ。……それに、凍てつくような絶望の中で足掻く貴様には、ひどく興味を惹かれるのでな」</t>
+  </si>
+  <si>
+    <t>悪魔の冷たい指先が、紫苑の頬をそっと撫でた。</t>
+  </si>
+  <si>
+    <t>呆れるほど尊大で、底知れない力を持った悪魔からの猛アピール。</t>
+  </si>
+  <si>
+    <t>最後の一撃が深々と突き刺さり、氷像全体を震わせる。鼓膜を劈くような甲高い亀裂音が神殿に響き渡った。</t>
+    <rPh sb="3" eb="5">
+      <t>イチゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウゾウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>フル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>透き通るような氷を纏った悪魔は、息を切らして膝をつく紫苑を見下ろし、酷薄な唇に艶やかな笑みを浮かべる。</t>
+    <rPh sb="12" eb="14">
+      <t>アクマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「……これで、終わりか。それじゃあ、あなたとの契約もここまでかな」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アルカナの導き次第では、余が直接その盤面に降り立ち、助力を与えてやってもよいぞ。せいぜい楽しみに待っていることだ。……何なら、今からでも手伝ってやろうか？」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫苑は冷たい空気を肺に吸い込み、やれやれと小さく息をついた。どうやら、この悪魔とは、まだ長い付き合いになりそうだ。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3765,6 +3927,183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64A577B-5BB8-4CF4-8A0F-C0F786591683}">
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>385</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B38310-6FC5-4CEC-90C4-F48C7825049A}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>407</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6DA5-2661-4E45-AB92-D2EA5AC3D0F2}">
   <dimension ref="A1:A53"/>
